--- a/medical_surveys_questionnaires/038_kidney_health_assessment_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/038_kidney_health_assessment_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'diabetes_mellitus'}</t>
+          <t>diabetes_mellitus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Diabetes Mellitus'}</t>
+          <t>Diabetes Mellitus</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'chronic_kidney_disease'}</t>
+          <t>chronic_kidney_disease</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Chronic Kidney Disease'}</t>
+          <t>Chronic Kidney Disease</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other_medical_condition'}</t>
+          <t>other_medical_condition</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other Medical Condition'}</t>
+          <t>Other Medical Condition</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'siblings'}</t>
+          <t>siblings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Siblings'}</t>
+          <t>Siblings</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hemoglobin'}</t>
+          <t>hemoglobin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Hemoglobin'}</t>
+          <t>Hemoglobin</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'creatinine'}</t>
+          <t>creatinine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Creatinine'}</t>
+          <t>Creatinine</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'urea'}</t>
+          <t>urea</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Urea'}</t>
+          <t>Urea</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'stage_1'}</t>
+          <t>stage_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Stage 1'}</t>
+          <t>Stage 1</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'stage_2'}</t>
+          <t>stage_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Stage 2'}</t>
+          <t>Stage 2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'stage_3'}</t>
+          <t>stage_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Stage 3'}</t>
+          <t>Stage 3</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasional'}</t>
+          <t>Occasional</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasional'}</t>
+          <t>Occasional</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasional'}</t>
+          <t>Occasional</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'balanced'}</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Balanced'}</t>
+          <t>Balanced</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unbalanced'}</t>
+          <t>unbalanced</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unbalanced'}</t>
+          <t>Unbalanced</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'overweight'}</t>
+          <t>overweight</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Overweight'}</t>
+          <t>Overweight</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'obese'}</t>
+          <t>obese</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Obese'}</t>
+          <t>Obese</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'underweight'}</t>
+          <t>underweight</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Underweight'}</t>
+          <t>Underweight</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'abnormal'}</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Abnormal'}</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
